--- a/Financial Analysis/RIVN.xlsx
+++ b/Financial Analysis/RIVN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3406EBC7-17E6-48CF-9A1C-432D987F67F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732BC78D-AEE9-4458-A13D-613874B3A2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{ABF471AF-A41B-460E-88DC-31087F0CAAFB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{ABF471AF-A41B-460E-88DC-31087F0CAAFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -864,14 +864,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>13.57</v>
+        <v>12.68</v>
       </c>
       <c r="E3" s="5">
-        <v>45899</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45925</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="5">
         <v>45966</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>16465.838000000003</v>
+        <v>15385.912</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>13206.838000000003</v>
+        <v>12126.912</v>
       </c>
     </row>
   </sheetData>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AN36" s="4">
         <f>Main!D3</f>
-        <v>13.57</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="37" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AN37" s="11">
         <f>AN35/AN36-1</f>
-        <v>-1.0545520217956506</v>
+        <v>-1.0583809886251561</v>
       </c>
     </row>
     <row r="38" spans="2:40" x14ac:dyDescent="0.3">
@@ -6189,13 +6189,13 @@
     <row r="81" spans="40:40" x14ac:dyDescent="0.3">
       <c r="AN81" s="4">
         <f>Main!D3</f>
-        <v>13.57</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="82" spans="40:40" x14ac:dyDescent="0.3">
       <c r="AN82" s="11">
         <f>AN80/AN81-1</f>
-        <v>-0.77098230893300101</v>
+        <v>-0.75490772336126366</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RIVN.xlsx
+++ b/Financial Analysis/RIVN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732BC78D-AEE9-4458-A13D-613874B3A2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2911827-07B1-4A79-9E3E-82E95C20FF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{ABF471AF-A41B-460E-88DC-31087F0CAAFB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{ABF471AF-A41B-460E-88DC-31087F0CAAFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="95">
   <si>
     <t>RIVN</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Software Margin</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -439,14 +442,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -463,7 +466,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10561320" y="7620"/>
+          <a:off x="11163300" y="7620"/>
           <a:ext cx="0" cy="16009620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -864,17 +867,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>12.68</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="E3" s="5">
-        <v>45965</v>
+        <v>46002</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45965</v>
+        <v>46002</v>
       </c>
       <c r="G3" s="5">
-        <v>45966</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -882,11 +885,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>1209.5+3.9</f>
-        <v>1213.4000000000001</v>
+        <f>1222+3.9</f>
+        <v>1225.9000000000001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -895,7 +898,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>15385.912</v>
+        <v>20043.465000000004</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -903,11 +906,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>5294+2406</f>
-        <v>7700</v>
+        <f>4441+2647</f>
+        <v>7088</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -915,11 +918,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>4441</f>
-        <v>4441</v>
+        <f>4438</f>
+        <v>4438</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -928,7 +931,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>3259</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -937,7 +940,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>12126.912</v>
+        <v>17393.465000000004</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17E2D89C-980A-401A-89E6-595EDF92B56B}">
-  <dimension ref="B2:EJ82"/>
+  <dimension ref="B2:EJ83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1076,7 +1079,9 @@
       <c r="L3" s="7">
         <v>1074</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="8">
+        <v>776</v>
+      </c>
       <c r="N3" s="8">
         <v>1520</v>
       </c>
@@ -1086,55 +1091,60 @@
       <c r="P3" s="7">
         <v>927</v>
       </c>
-      <c r="Q3" s="7">
-        <v>800</v>
-      </c>
-      <c r="R3" s="7">
-        <v>1500</v>
+      <c r="Q3" s="8">
+        <v>1142</v>
+      </c>
+      <c r="R3" s="8">
+        <f>N3*1.1</f>
+        <v>1672.0000000000002</v>
+      </c>
+      <c r="Y3" s="6">
+        <f>SUM(K3:N3)</f>
+        <v>4486</v>
       </c>
       <c r="Z3" s="6">
         <f>SUM(O3:R3)</f>
-        <v>4149</v>
+        <v>4663</v>
       </c>
       <c r="AA3" s="6">
         <f>Z3*1.3</f>
-        <v>5393.7</v>
+        <v>6061.9000000000005</v>
       </c>
       <c r="AB3" s="6">
         <f>AA3*1.2</f>
-        <v>6472.44</v>
+        <v>7274.2800000000007</v>
       </c>
       <c r="AC3" s="6">
-        <f t="shared" ref="AC3:AI3" si="0">AB3*1.15</f>
-        <v>7443.3059999999987</v>
+        <f t="shared" ref="AC3:AI4" si="0">AB3*1.15</f>
+        <v>8365.4220000000005</v>
       </c>
       <c r="AD3" s="6">
         <f t="shared" si="0"/>
-        <v>8559.8018999999986</v>
+        <v>9620.2353000000003</v>
       </c>
       <c r="AE3" s="6">
         <f t="shared" si="0"/>
-        <v>9843.772184999998</v>
+        <v>11063.270595</v>
       </c>
       <c r="AF3" s="6">
         <f t="shared" si="0"/>
-        <v>11320.338012749997</v>
+        <v>12722.761184249999</v>
       </c>
       <c r="AG3" s="6">
         <f t="shared" si="0"/>
-        <v>13018.388714662495</v>
+        <v>14631.175361887497</v>
       </c>
       <c r="AH3" s="6">
         <f t="shared" si="0"/>
-        <v>14971.147021861867</v>
+        <v>16825.85166617062</v>
       </c>
       <c r="AI3" s="6">
         <f t="shared" si="0"/>
-        <v>17216.819075141146</v>
+        <v>19349.729416096212</v>
       </c>
       <c r="AJ3" s="6">
         <f>AI3*1.1</f>
-        <v>18938.500982655263</v>
+        <v>21284.702357705835</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1157,7 +1167,9 @@
       <c r="L4" s="7">
         <v>84</v>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="8">
+        <v>98</v>
+      </c>
       <c r="N4" s="8">
         <v>214</v>
       </c>
@@ -1167,55 +1179,60 @@
       <c r="P4" s="7">
         <v>376</v>
       </c>
-      <c r="Q4" s="7">
-        <v>320</v>
-      </c>
-      <c r="R4" s="7">
-        <v>420</v>
+      <c r="Q4" s="8">
+        <v>416</v>
+      </c>
+      <c r="R4" s="8">
+        <f>N4*2.5</f>
+        <v>535</v>
+      </c>
+      <c r="Y4" s="6">
+        <f>SUM(K4:N4)</f>
+        <v>484</v>
       </c>
       <c r="Z4" s="6">
         <f>SUM(O4:R4)</f>
-        <v>1434</v>
+        <v>1645</v>
       </c>
       <c r="AA4" s="6">
         <f>Z4*1.3</f>
-        <v>1864.2</v>
+        <v>2138.5</v>
       </c>
       <c r="AB4" s="6">
         <f>AA4*1.2</f>
-        <v>2237.04</v>
+        <v>2566.1999999999998</v>
       </c>
       <c r="AC4" s="6">
         <f>AB4*1.15</f>
-        <v>2572.5959999999995</v>
+        <v>2951.1299999999997</v>
       </c>
       <c r="AD4" s="6">
-        <f>AC4*1.1</f>
-        <v>2829.8555999999999</v>
+        <f>AC4*1.15</f>
+        <v>3393.7994999999992</v>
       </c>
       <c r="AE4" s="6">
-        <f>AD4*1.05</f>
-        <v>2971.3483799999999</v>
+        <f t="shared" si="0"/>
+        <v>3902.869424999999</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" ref="AF4:AJ4" si="1">AE4*1.05</f>
-        <v>3119.9157989999999</v>
+        <f t="shared" si="0"/>
+        <v>4488.2998387499983</v>
       </c>
       <c r="AG4" s="6">
-        <f t="shared" si="1"/>
-        <v>3275.9115889499999</v>
+        <f t="shared" si="0"/>
+        <v>5161.5448145624978</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="1"/>
-        <v>3439.7071683975</v>
+        <f t="shared" si="0"/>
+        <v>5935.7765367468719</v>
       </c>
       <c r="AI4" s="6">
-        <f t="shared" si="1"/>
-        <v>3611.692526817375</v>
+        <f t="shared" si="0"/>
+        <v>6826.1430172589025</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" si="1"/>
-        <v>3792.2771531582439</v>
+        <f t="shared" ref="AJ4" si="1">AI4*1.15</f>
+        <v>7850.0644698477372</v>
       </c>
     </row>
     <row r="5" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1259,11 +1276,11 @@
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>1120</v>
+        <v>1558</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="3"/>
-        <v>1920</v>
+        <v>2207</v>
       </c>
       <c r="U5" s="9">
         <v>0</v>
@@ -1284,47 +1301,47 @@
       </c>
       <c r="Z5" s="9">
         <f>Z3+Z4</f>
-        <v>5583</v>
+        <v>6308</v>
       </c>
       <c r="AA5" s="9">
         <f t="shared" ref="AA5:AJ5" si="4">AA3+AA4</f>
-        <v>7257.9</v>
+        <v>8200.4000000000015</v>
       </c>
       <c r="AB5" s="9">
         <f t="shared" si="4"/>
-        <v>8709.48</v>
+        <v>9840.48</v>
       </c>
       <c r="AC5" s="9">
         <f t="shared" si="4"/>
-        <v>10015.901999999998</v>
+        <v>11316.552</v>
       </c>
       <c r="AD5" s="9">
         <f t="shared" si="4"/>
-        <v>11389.657499999998</v>
+        <v>13014.034799999999</v>
       </c>
       <c r="AE5" s="9">
         <f t="shared" si="4"/>
-        <v>12815.120564999997</v>
+        <v>14966.140019999999</v>
       </c>
       <c r="AF5" s="9">
         <f t="shared" si="4"/>
-        <v>14440.253811749997</v>
+        <v>17211.061022999998</v>
       </c>
       <c r="AG5" s="9">
         <f t="shared" si="4"/>
-        <v>16294.300303612494</v>
+        <v>19792.720176449995</v>
       </c>
       <c r="AH5" s="9">
         <f t="shared" si="4"/>
-        <v>18410.854190259368</v>
+        <v>22761.628202917491</v>
       </c>
       <c r="AI5" s="9">
         <f t="shared" si="4"/>
-        <v>20828.511601958522</v>
+        <v>26175.872433355114</v>
       </c>
       <c r="AJ5" s="9">
         <f t="shared" si="4"/>
-        <v>22730.778135813507</v>
+        <v>29134.766827553573</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1354,12 +1371,11 @@
         <v>1262</v>
       </c>
       <c r="Q6" s="6">
-        <f>Q3*0.87</f>
-        <v>696</v>
+        <v>1272</v>
       </c>
       <c r="R6" s="6">
         <f t="shared" ref="R6" si="5">R3*0.88</f>
-        <v>1320</v>
+        <v>1471.3600000000001</v>
       </c>
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
@@ -1368,47 +1384,47 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6">
         <f t="shared" ref="Z6:Z7" si="6">SUM(O6:R6)</f>
-        <v>4108</v>
+        <v>4835.3600000000006</v>
       </c>
       <c r="AA6" s="6">
-        <f>AA3*0.86</f>
-        <v>4638.5819999999994</v>
+        <f>AA3*0.92</f>
+        <v>5576.9480000000003</v>
       </c>
       <c r="AB6" s="6">
-        <f>AB3*0.85</f>
-        <v>5501.5739999999996</v>
+        <f>AB3*0.88</f>
+        <v>6401.3664000000008</v>
       </c>
       <c r="AC6" s="6">
-        <f>AC3*0.84</f>
-        <v>6252.3770399999985</v>
+        <f>AC3*0.85</f>
+        <v>7110.6086999999998</v>
       </c>
       <c r="AD6" s="6">
         <f>AD3*0.83</f>
-        <v>7104.6355769999982</v>
+        <v>7984.7952989999994</v>
       </c>
       <c r="AE6" s="6">
         <f>AE3*0.82</f>
-        <v>8071.8931916999982</v>
+        <v>9071.8818878999991</v>
       </c>
       <c r="AF6" s="6">
         <f>AF3*0.81</f>
-        <v>9169.4737903274981</v>
+        <v>10305.4365592425</v>
       </c>
       <c r="AG6" s="6">
         <f t="shared" ref="AG6:AJ6" si="7">AG3*0.81</f>
-        <v>10544.894858876622</v>
+        <v>11851.252043128874</v>
       </c>
       <c r="AH6" s="6">
         <f t="shared" si="7"/>
-        <v>12126.629087708114</v>
+        <v>13628.939849598202</v>
       </c>
       <c r="AI6" s="6">
         <f t="shared" si="7"/>
-        <v>13945.623450864328</v>
+        <v>15673.280827037932</v>
       </c>
       <c r="AJ6" s="6">
         <f t="shared" si="7"/>
-        <v>15340.185795950763</v>
+        <v>17240.608909741728</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
@@ -1438,12 +1454,11 @@
         <v>247</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" ref="Q7:R7" si="8">Q4*0.6</f>
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="R7" s="6">
-        <f t="shared" si="8"/>
-        <v>252</v>
+        <f t="shared" ref="R7" si="8">R4*0.6</f>
+        <v>321</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
@@ -1452,47 +1467,47 @@
       <c r="Y7" s="8"/>
       <c r="Z7" s="6">
         <f t="shared" si="6"/>
-        <v>895</v>
+        <v>1034</v>
       </c>
       <c r="AA7" s="6">
         <f>AA4*0.6</f>
-        <v>1118.52</v>
+        <v>1283.0999999999999</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" ref="AB7:AJ7" si="9">AB4*0.6</f>
-        <v>1342.2239999999999</v>
+        <f>AB4*0.57</f>
+        <v>1462.7339999999997</v>
       </c>
       <c r="AC7" s="6">
-        <f t="shared" si="9"/>
-        <v>1543.5575999999996</v>
+        <f>AC4*0.55</f>
+        <v>1623.1215</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="9"/>
-        <v>1697.9133599999998</v>
+        <f>AD4*0.54</f>
+        <v>1832.6517299999996</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" si="9"/>
-        <v>1782.8090279999999</v>
+        <f>AE4*0.53</f>
+        <v>2068.5207952499995</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="9"/>
-        <v>1871.9494793999997</v>
+        <f t="shared" ref="AF7:AJ7" si="9">AF4*0.53</f>
+        <v>2378.7989145374991</v>
       </c>
       <c r="AG7" s="6">
         <f t="shared" si="9"/>
-        <v>1965.5469533699998</v>
+        <v>2735.6187517181238</v>
       </c>
       <c r="AH7" s="6">
         <f t="shared" si="9"/>
-        <v>2063.8243010384999</v>
+        <v>3145.9615644758424</v>
       </c>
       <c r="AI7" s="6">
         <f t="shared" si="9"/>
-        <v>2167.0155160904251</v>
+        <v>3617.8557991472185</v>
       </c>
       <c r="AJ7" s="6">
         <f t="shared" si="9"/>
-        <v>2275.3662918949462</v>
+        <v>4160.5341690193009</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
@@ -1536,11 +1551,11 @@
       </c>
       <c r="Q8" s="8">
         <f t="shared" si="10"/>
-        <v>888</v>
+        <v>1534</v>
       </c>
       <c r="R8" s="8">
         <f t="shared" si="10"/>
-        <v>1572</v>
+        <v>1792.3600000000001</v>
       </c>
       <c r="U8" s="6">
         <v>0</v>
@@ -1561,47 +1576,47 @@
       </c>
       <c r="Z8" s="6">
         <f>Z6+Z7</f>
-        <v>5003</v>
+        <v>5869.3600000000006</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" ref="AA8:AJ8" si="11">AA6+AA7</f>
-        <v>5757.101999999999</v>
+        <v>6860.0480000000007</v>
       </c>
       <c r="AB8" s="6">
         <f t="shared" si="11"/>
-        <v>6843.7979999999998</v>
+        <v>7864.1004000000003</v>
       </c>
       <c r="AC8" s="6">
         <f t="shared" si="11"/>
-        <v>7795.9346399999977</v>
+        <v>8733.7302</v>
       </c>
       <c r="AD8" s="6">
         <f t="shared" si="11"/>
-        <v>8802.5489369999977</v>
+        <v>9817.447028999999</v>
       </c>
       <c r="AE8" s="6">
         <f t="shared" si="11"/>
-        <v>9854.7022196999988</v>
+        <v>11140.402683149998</v>
       </c>
       <c r="AF8" s="6">
         <f t="shared" si="11"/>
-        <v>11041.423269727498</v>
+        <v>12684.23547378</v>
       </c>
       <c r="AG8" s="6">
         <f t="shared" si="11"/>
-        <v>12510.441812246621</v>
+        <v>14586.870794846998</v>
       </c>
       <c r="AH8" s="6">
         <f t="shared" si="11"/>
-        <v>14190.453388746613</v>
+        <v>16774.901414074044</v>
       </c>
       <c r="AI8" s="6">
         <f t="shared" si="11"/>
-        <v>16112.638966954753</v>
+        <v>19291.136626185151</v>
       </c>
       <c r="AJ8" s="6">
         <f t="shared" si="11"/>
-        <v>17615.55208784571</v>
+        <v>21401.14307876103</v>
       </c>
     </row>
     <row r="9" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1650,11 +1665,11 @@
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="13"/>
-        <v>232</v>
+        <v>24</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="13"/>
-        <v>348</v>
+        <v>414.63999999999987</v>
       </c>
       <c r="U9" s="9">
         <f t="shared" ref="U9:AJ9" si="14">U5-U8</f>
@@ -1678,47 +1693,47 @@
       </c>
       <c r="Z9" s="9">
         <f t="shared" si="14"/>
-        <v>580</v>
+        <v>438.63999999999942</v>
       </c>
       <c r="AA9" s="9">
         <f t="shared" si="14"/>
-        <v>1500.7980000000007</v>
+        <v>1340.3520000000008</v>
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="14"/>
-        <v>1865.6819999999998</v>
+        <v>1976.3795999999993</v>
       </c>
       <c r="AC9" s="9">
         <f t="shared" si="14"/>
-        <v>2219.9673600000006</v>
+        <v>2582.8217999999997</v>
       </c>
       <c r="AD9" s="9">
         <f t="shared" si="14"/>
-        <v>2587.1085629999998</v>
+        <v>3196.5877710000004</v>
       </c>
       <c r="AE9" s="9">
         <f t="shared" si="14"/>
-        <v>2960.4183452999987</v>
+        <v>3825.7373368500012</v>
       </c>
       <c r="AF9" s="9">
         <f t="shared" si="14"/>
-        <v>3398.8305420224988</v>
+        <v>4526.8255492199987</v>
       </c>
       <c r="AG9" s="9">
         <f t="shared" si="14"/>
-        <v>3783.8584913658724</v>
+        <v>5205.8493816029968</v>
       </c>
       <c r="AH9" s="9">
         <f t="shared" si="14"/>
-        <v>4220.4008015127547</v>
+        <v>5986.7267888434471</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="14"/>
-        <v>4715.8726350037687</v>
+        <v>6884.7358071699637</v>
       </c>
       <c r="AJ9" s="9">
         <f t="shared" si="14"/>
-        <v>5115.2260479677971</v>
+        <v>7733.6237487925428</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1756,12 +1771,11 @@
         <v>410</v>
       </c>
       <c r="Q10" s="6">
-        <f>P10*0.9</f>
-        <v>369</v>
+        <v>453</v>
       </c>
       <c r="R10" s="6">
-        <f>P10*1.05</f>
-        <v>430.5</v>
+        <f>P10*1.15</f>
+        <v>471.49999999999994</v>
       </c>
       <c r="U10" s="6">
         <v>766</v>
@@ -1782,47 +1796,47 @@
       </c>
       <c r="Z10" s="6">
         <f>SUM(O10:R10)</f>
-        <v>1590.5</v>
+        <v>1715.5</v>
       </c>
       <c r="AA10" s="6">
         <f>Z10*1.04</f>
-        <v>1654.1200000000001</v>
+        <v>1784.1200000000001</v>
       </c>
       <c r="AB10" s="6">
         <f>AA10*1.03</f>
-        <v>1703.7436000000002</v>
+        <v>1837.6436000000001</v>
       </c>
       <c r="AC10" s="6">
         <f>AB10*1.02</f>
-        <v>1737.8184720000004</v>
+        <v>1874.3964720000001</v>
       </c>
       <c r="AD10" s="6">
         <f t="shared" ref="AD10" si="15">AC10*1.02</f>
-        <v>1772.5748414400005</v>
+        <v>1911.8844014400001</v>
       </c>
       <c r="AE10" s="6">
         <f>AD10*1.01</f>
-        <v>1790.3005898544004</v>
+        <v>1931.0032454544003</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" ref="AF10:AJ11" si="16">AE10*1.01</f>
-        <v>1808.2035957529445</v>
+        <v>1950.3132779089442</v>
       </c>
       <c r="AG10" s="6">
         <f t="shared" si="16"/>
-        <v>1826.285631710474</v>
+        <v>1969.8164106880336</v>
       </c>
       <c r="AH10" s="6">
         <f t="shared" si="16"/>
-        <v>1844.5484880275787</v>
+        <v>1989.5145747949139</v>
       </c>
       <c r="AI10" s="6">
         <f t="shared" si="16"/>
-        <v>1862.9939729078546</v>
+        <v>2009.4097205428629</v>
       </c>
       <c r="AJ10" s="6">
         <f t="shared" si="16"/>
-        <v>1881.6239126369333</v>
+        <v>2029.5038177482916</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1860,12 +1874,11 @@
         <v>498</v>
       </c>
       <c r="Q11" s="6">
-        <f>P11*1.02</f>
-        <v>507.96000000000004</v>
+        <v>554</v>
       </c>
       <c r="R11" s="6">
-        <f>Q11*1.01</f>
-        <v>513.03960000000006</v>
+        <f>Q11*1.03</f>
+        <v>570.62</v>
       </c>
       <c r="U11" s="6">
         <v>255</v>
@@ -1887,47 +1900,47 @@
       </c>
       <c r="Z11" s="6">
         <f>SUM(O11:R11)</f>
-        <v>1998.9996000000001</v>
+        <v>2102.62</v>
       </c>
       <c r="AA11" s="6">
         <f>Z11*1.03</f>
-        <v>2058.9695879999999</v>
+        <v>2165.6986000000002</v>
       </c>
       <c r="AB11" s="6">
         <f>AA11*1.02</f>
-        <v>2100.1489797599997</v>
+        <v>2209.0125720000001</v>
       </c>
       <c r="AC11" s="6">
         <f>AB11*1.01</f>
-        <v>2121.1504695576</v>
+        <v>2231.1026977199999</v>
       </c>
       <c r="AD11" s="6">
         <f t="shared" ref="AD11:AE11" si="17">AC11*1.01</f>
-        <v>2142.361974253176</v>
+        <v>2253.4137246972</v>
       </c>
       <c r="AE11" s="6">
         <f t="shared" si="17"/>
-        <v>2163.7855939957076</v>
+        <v>2275.947861944172</v>
       </c>
       <c r="AF11" s="6">
         <f t="shared" si="16"/>
-        <v>2185.4234499356648</v>
+        <v>2298.7073405636138</v>
       </c>
       <c r="AG11" s="6">
         <f t="shared" si="16"/>
-        <v>2207.2776844350215</v>
+        <v>2321.69441396925</v>
       </c>
       <c r="AH11" s="6">
         <f t="shared" si="16"/>
-        <v>2229.3504612793718</v>
+        <v>2344.9113581089427</v>
       </c>
       <c r="AI11" s="6">
         <f t="shared" si="16"/>
-        <v>2251.6439658921654</v>
+        <v>2368.3604716900322</v>
       </c>
       <c r="AJ11" s="6">
         <f t="shared" si="16"/>
-        <v>2274.160405551087</v>
+        <v>2392.0440764069326</v>
       </c>
     </row>
     <row r="12" spans="2:36" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1976,11 +1989,11 @@
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="19"/>
-        <v>-644.96</v>
+        <v>-983</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="19"/>
-        <v>-595.53960000000006</v>
+        <v>-627.48</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" ref="U12:Z12" si="20">U9-U10-U11</f>
@@ -2004,47 +2017,47 @@
       </c>
       <c r="Z12" s="9">
         <f t="shared" si="20"/>
-        <v>-3009.4996000000001</v>
+        <v>-3379.4800000000005</v>
       </c>
       <c r="AA12" s="9">
         <f t="shared" ref="AA12:AJ12" si="21">AA9-AA10-AA11</f>
-        <v>-2212.2915879999991</v>
+        <v>-2609.4665999999997</v>
       </c>
       <c r="AB12" s="9">
         <f t="shared" si="21"/>
-        <v>-1938.2105797600002</v>
+        <v>-2070.2765720000007</v>
       </c>
       <c r="AC12" s="9">
         <f t="shared" si="21"/>
-        <v>-1639.0015815575998</v>
+        <v>-1522.6773697200003</v>
       </c>
       <c r="AD12" s="9">
         <f t="shared" si="21"/>
-        <v>-1327.8282526931766</v>
+        <v>-968.71035513719971</v>
       </c>
       <c r="AE12" s="9">
         <f t="shared" si="21"/>
-        <v>-993.66783855010931</v>
+        <v>-381.21377054857112</v>
       </c>
       <c r="AF12" s="9">
         <f t="shared" si="21"/>
-        <v>-594.79650366611054</v>
+        <v>277.80493074744072</v>
       </c>
       <c r="AG12" s="9">
         <f t="shared" si="21"/>
-        <v>-249.7048247796231</v>
+        <v>914.33855694571321</v>
       </c>
       <c r="AH12" s="9">
         <f t="shared" si="21"/>
-        <v>146.50185220580397</v>
+        <v>1652.3008559395907</v>
       </c>
       <c r="AI12" s="9">
         <f t="shared" si="21"/>
-        <v>601.23469620374863</v>
+        <v>2506.9656149370689</v>
       </c>
       <c r="AJ12" s="9">
         <f t="shared" si="21"/>
-        <v>959.44172977977678</v>
+        <v>3312.075854637319</v>
       </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.3">
@@ -2082,11 +2095,10 @@
         <v>-72</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" ref="Q13:R13" si="22">M13*1.03</f>
-        <v>-97.850000000000009</v>
+        <v>-76</v>
       </c>
       <c r="R13" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="R13" si="22">N13*1.03</f>
         <v>-85.490000000000009</v>
       </c>
       <c r="U13" s="6">
@@ -2108,47 +2120,47 @@
       </c>
       <c r="Z13" s="6">
         <f>SUM(O13:R13)</f>
-        <v>-336.34000000000003</v>
+        <v>-314.49</v>
       </c>
       <c r="AA13" s="6">
         <f>Z13*1.03</f>
-        <v>-346.43020000000001</v>
+        <v>-323.92470000000003</v>
       </c>
       <c r="AB13" s="6">
         <f t="shared" ref="AB13:AJ13" si="23">AA13*1.03</f>
-        <v>-356.823106</v>
+        <v>-333.64244100000002</v>
       </c>
       <c r="AC13" s="6">
         <f t="shared" si="23"/>
-        <v>-367.52779917999999</v>
+        <v>-343.65171423000004</v>
       </c>
       <c r="AD13" s="6">
         <f t="shared" si="23"/>
-        <v>-378.55363315540001</v>
+        <v>-353.96126565690003</v>
       </c>
       <c r="AE13" s="6">
         <f t="shared" si="23"/>
-        <v>-389.910242150062</v>
+        <v>-364.58010362660701</v>
       </c>
       <c r="AF13" s="6">
         <f t="shared" si="23"/>
-        <v>-401.60754941456389</v>
+        <v>-375.51750673540522</v>
       </c>
       <c r="AG13" s="6">
         <f t="shared" si="23"/>
-        <v>-413.65577589700081</v>
+        <v>-386.7830319374674</v>
       </c>
       <c r="AH13" s="6">
         <f t="shared" si="23"/>
-        <v>-426.06544917391085</v>
+        <v>-398.38652289559144</v>
       </c>
       <c r="AI13" s="6">
         <f t="shared" si="23"/>
-        <v>-438.84741264912816</v>
+        <v>-410.33811858245917</v>
       </c>
       <c r="AJ13" s="6">
         <f t="shared" si="23"/>
-        <v>-452.01283502860201</v>
+        <v>-422.64826213993297</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
@@ -2186,7 +2198,7 @@
         <v>69</v>
       </c>
       <c r="Q14" s="6">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="R14" s="6">
         <v>82</v>
@@ -2210,47 +2222,47 @@
       </c>
       <c r="Z14" s="6">
         <f>SUM(O14:R14)</f>
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="AA14" s="6">
         <f>Z14*1.02</f>
-        <v>311.10000000000002</v>
+        <v>297.84000000000003</v>
       </c>
       <c r="AB14" s="6">
         <f t="shared" ref="AB14:AJ14" si="24">AA14*1.02</f>
-        <v>317.322</v>
+        <v>303.79680000000002</v>
       </c>
       <c r="AC14" s="6">
         <f t="shared" si="24"/>
-        <v>323.66844000000003</v>
+        <v>309.87273600000003</v>
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="24"/>
-        <v>330.14180880000004</v>
+        <v>316.07019072000003</v>
       </c>
       <c r="AE14" s="6">
         <f t="shared" si="24"/>
-        <v>336.74464497600002</v>
+        <v>322.39159453440004</v>
       </c>
       <c r="AF14" s="6">
         <f t="shared" si="24"/>
-        <v>343.47953787552001</v>
+        <v>328.83942642508805</v>
       </c>
       <c r="AG14" s="6">
         <f t="shared" si="24"/>
-        <v>350.34912863303043</v>
+        <v>335.41621495358982</v>
       </c>
       <c r="AH14" s="6">
         <f t="shared" si="24"/>
-        <v>357.35611120569104</v>
+        <v>342.12453925266163</v>
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="24"/>
-        <v>364.50323342980488</v>
+        <v>348.96703003771489</v>
       </c>
       <c r="AJ14" s="6">
         <f t="shared" si="24"/>
-        <v>371.79329809840101</v>
+        <v>355.9463706384692</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.3">
@@ -2380,7 +2392,7 @@
         <v>2</v>
       </c>
       <c r="Q16" s="6">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="R16" s="6">
         <v>0</v>
@@ -2404,7 +2416,7 @@
       </c>
       <c r="Z16" s="6">
         <f>SUM(O16:R16)</f>
-        <v>-105</v>
+        <v>86</v>
       </c>
       <c r="AA16" s="6">
         <v>0</v>
@@ -2483,7 +2495,7 @@
       </c>
       <c r="Q17" s="6">
         <f t="shared" si="26"/>
-        <v>-15.850000000000009</v>
+        <v>184</v>
       </c>
       <c r="R17" s="6">
         <f t="shared" si="26"/>
@@ -2511,47 +2523,47 @@
       </c>
       <c r="Z17" s="6">
         <f t="shared" si="27"/>
-        <v>-136.34000000000003</v>
+        <v>63.509999999999991</v>
       </c>
       <c r="AA17" s="6">
         <f t="shared" si="27"/>
-        <v>-35.330199999999991</v>
+        <v>-26.084699999999998</v>
       </c>
       <c r="AB17" s="6">
         <f t="shared" ref="AB17:AJ17" si="28">SUM(AB13:AB16)</f>
-        <v>-39.501105999999993</v>
+        <v>-29.845641000000001</v>
       </c>
       <c r="AC17" s="6">
         <f t="shared" si="28"/>
-        <v>-43.859359179999956</v>
+        <v>-33.778978230000007</v>
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="28"/>
-        <v>-48.411824355399972</v>
+        <v>-37.891074936899997</v>
       </c>
       <c r="AE17" s="6">
         <f t="shared" si="28"/>
-        <v>-53.165597174061986</v>
+        <v>-42.188509092206971</v>
       </c>
       <c r="AF17" s="6">
         <f t="shared" si="28"/>
-        <v>-58.128011539043882</v>
+        <v>-46.678080310317171</v>
       </c>
       <c r="AG17" s="6">
         <f t="shared" si="28"/>
-        <v>-63.306647263970376</v>
+        <v>-51.366816983877584</v>
       </c>
       <c r="AH17" s="6">
         <f t="shared" si="28"/>
-        <v>-68.709337968219813</v>
+        <v>-56.261983642929806</v>
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="28"/>
-        <v>-74.34417921932328</v>
+        <v>-61.371088544744282</v>
       </c>
       <c r="AJ17" s="6">
         <f t="shared" si="28"/>
-        <v>-80.219536930201002</v>
+        <v>-66.701891501463763</v>
       </c>
     </row>
     <row r="18" spans="2:136" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2600,11 +2612,11 @@
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="30"/>
-        <v>-629.11</v>
+        <v>-1167</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="30"/>
-        <v>-592.04960000000005</v>
+        <v>-623.99</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" ref="U18:AA18" si="31">U12-U17</f>
@@ -2628,47 +2640,47 @@
       </c>
       <c r="Z18" s="9">
         <f t="shared" si="31"/>
-        <v>-2873.1596</v>
+        <v>-3442.9900000000007</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="31"/>
-        <v>-2176.9613879999993</v>
+        <v>-2583.3818999999999</v>
       </c>
       <c r="AB18" s="9">
         <f t="shared" ref="AB18:AJ18" si="32">AB12-AB17</f>
-        <v>-1898.7094737600003</v>
+        <v>-2040.4309310000008</v>
       </c>
       <c r="AC18" s="9">
         <f t="shared" si="32"/>
-        <v>-1595.1422223775999</v>
+        <v>-1488.8983914900004</v>
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="32"/>
-        <v>-1279.4164283377768</v>
+        <v>-930.81928020029977</v>
       </c>
       <c r="AE18" s="9">
         <f t="shared" si="32"/>
-        <v>-940.50224137604732</v>
+        <v>-339.02526145636415</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="32"/>
-        <v>-536.66849212706666</v>
+        <v>324.48301105775789</v>
       </c>
       <c r="AG18" s="9">
         <f t="shared" si="32"/>
-        <v>-186.39817751565272</v>
+        <v>965.70537392959079</v>
       </c>
       <c r="AH18" s="9">
         <f t="shared" si="32"/>
-        <v>215.21119017402378</v>
+        <v>1708.5628395825206</v>
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="32"/>
-        <v>675.57887542307185</v>
+        <v>2568.3367034818134</v>
       </c>
       <c r="AJ18" s="9">
         <f t="shared" si="32"/>
-        <v>1039.6612667099778</v>
+        <v>3378.7777461387827</v>
       </c>
     </row>
     <row r="19" spans="2:136" x14ac:dyDescent="0.3">
@@ -2706,7 +2718,7 @@
         <v>2</v>
       </c>
       <c r="Q19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="6">
         <v>0</v>
@@ -2730,46 +2742,46 @@
       </c>
       <c r="Z19" s="6">
         <f>SUM(O19:R19)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA19" s="6">
         <v>0</v>
       </c>
       <c r="AB19" s="6">
         <f>AB18*0.2</f>
-        <v>-379.74189475200006</v>
+        <v>-408.08618620000016</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" ref="AC19:AJ19" si="33">AC18*0.2</f>
-        <v>-319.02844447552002</v>
+        <v>-297.77967829800008</v>
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="33"/>
-        <v>-255.88328566755536</v>
+        <v>-186.16385604005995</v>
       </c>
       <c r="AE19" s="6">
         <f t="shared" si="33"/>
-        <v>-188.10044827520949</v>
+        <v>-67.80505229127283</v>
       </c>
       <c r="AF19" s="6">
         <f t="shared" si="33"/>
-        <v>-107.33369842541333</v>
+        <v>64.896602211551581</v>
       </c>
       <c r="AG19" s="6">
         <f t="shared" si="33"/>
-        <v>-37.279635503130542</v>
+        <v>193.14107478591816</v>
       </c>
       <c r="AH19" s="6">
         <f t="shared" si="33"/>
-        <v>43.042238034804761</v>
+        <v>341.71256791650416</v>
       </c>
       <c r="AI19" s="6">
         <f t="shared" si="33"/>
-        <v>135.11577508461437</v>
+        <v>513.66734069636266</v>
       </c>
       <c r="AJ19" s="6">
         <f t="shared" si="33"/>
-        <v>207.93225334199556</v>
+        <v>675.75554922775655</v>
       </c>
     </row>
     <row r="20" spans="2:136" x14ac:dyDescent="0.3">
@@ -2807,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="Q20" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
@@ -2831,7 +2843,7 @@
       </c>
       <c r="Z20" s="6">
         <f>SUM(O20:R20)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AA20" s="6">
         <v>0</v>
@@ -2910,11 +2922,11 @@
       </c>
       <c r="Q21" s="9">
         <f t="shared" ref="Q21" si="37">Q18-Q19-Q20</f>
-        <v>-629.11</v>
+        <v>-1175</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" ref="R21" si="38">R18-R19-R20</f>
-        <v>-592.04960000000005</v>
+        <v>-623.99</v>
       </c>
       <c r="U21" s="9">
         <f t="shared" ref="U21:AA21" si="39">U18-U19-U20</f>
@@ -2938,447 +2950,447 @@
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="39"/>
-        <v>-2883.1596</v>
+        <v>-3460.9900000000007</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="39"/>
-        <v>-2176.9613879999993</v>
+        <v>-2583.3818999999999</v>
       </c>
       <c r="AB21" s="9">
         <f t="shared" ref="AB21:AJ21" si="40">AB18-AB19-AB20</f>
-        <v>-1518.9675790080003</v>
+        <v>-1632.3447448000006</v>
       </c>
       <c r="AC21" s="9">
         <f t="shared" si="40"/>
-        <v>-1276.1137779020798</v>
+        <v>-1191.1187131920003</v>
       </c>
       <c r="AD21" s="9">
         <f t="shared" si="40"/>
-        <v>-1023.5331426702214</v>
+        <v>-744.65542416023982</v>
       </c>
       <c r="AE21" s="9">
         <f t="shared" si="40"/>
-        <v>-752.40179310083784</v>
+        <v>-271.22020916509132</v>
       </c>
       <c r="AF21" s="9">
         <f t="shared" si="40"/>
-        <v>-429.33479370165333</v>
+        <v>259.58640884620633</v>
       </c>
       <c r="AG21" s="9">
         <f t="shared" si="40"/>
-        <v>-149.11854201252217</v>
+        <v>772.56429914367266</v>
       </c>
       <c r="AH21" s="9">
         <f t="shared" si="40"/>
-        <v>172.16895213921902</v>
+        <v>1366.8502716660164</v>
       </c>
       <c r="AI21" s="9">
         <f t="shared" si="40"/>
-        <v>540.46310033845748</v>
+        <v>2054.6693627854506</v>
       </c>
       <c r="AJ21" s="9">
         <f t="shared" si="40"/>
-        <v>831.72901336798225</v>
+        <v>2703.0221969110262</v>
       </c>
       <c r="AK21" s="3">
         <f>AJ21*(1+$AN$30)</f>
-        <v>823.41172323430237</v>
+        <v>2675.9919749419159</v>
       </c>
       <c r="AL21" s="3">
         <f t="shared" ref="AL21:CW21" si="41">AK21*(1+$AN$30)</f>
-        <v>815.17760600195936</v>
+        <v>2649.2320551924968</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="41"/>
-        <v>807.02582994193972</v>
+        <v>2622.7397346405719</v>
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="41"/>
-        <v>798.95557164252034</v>
+        <v>2596.5123372941662</v>
       </c>
       <c r="AO21" s="3">
         <f t="shared" si="41"/>
-        <v>790.96601592609511</v>
+        <v>2570.5472139212243</v>
       </c>
       <c r="AP21" s="3">
         <f t="shared" si="41"/>
-        <v>783.05635576683414</v>
+        <v>2544.8417417820119</v>
       </c>
       <c r="AQ21" s="3">
         <f t="shared" si="41"/>
-        <v>775.22579220916577</v>
+        <v>2519.3933243641918</v>
       </c>
       <c r="AR21" s="3">
         <f t="shared" si="41"/>
-        <v>767.47353428707413</v>
+        <v>2494.19939112055</v>
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="41"/>
-        <v>759.79879894420333</v>
+        <v>2469.2573972093446</v>
       </c>
       <c r="AT21" s="3">
         <f t="shared" si="41"/>
-        <v>752.20081095476132</v>
+        <v>2444.5648232372509</v>
       </c>
       <c r="AU21" s="3">
         <f t="shared" si="41"/>
-        <v>744.67880284521368</v>
+        <v>2420.1191750048783</v>
       </c>
       <c r="AV21" s="3">
         <f t="shared" si="41"/>
-        <v>737.23201481676153</v>
+        <v>2395.9179832548293</v>
       </c>
       <c r="AW21" s="3">
         <f t="shared" si="41"/>
-        <v>729.85969466859387</v>
+        <v>2371.9588034222811</v>
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="41"/>
-        <v>722.56109772190791</v>
+        <v>2348.2392153880583</v>
       </c>
       <c r="AY21" s="3">
         <f t="shared" si="41"/>
-        <v>715.33548674468886</v>
+        <v>2324.7568232341778</v>
       </c>
       <c r="AZ21" s="3">
         <f t="shared" si="41"/>
-        <v>708.182131877242</v>
+        <v>2301.5092550018358</v>
       </c>
       <c r="BA21" s="3">
         <f t="shared" si="41"/>
-        <v>701.10031055846957</v>
+        <v>2278.4941624518174</v>
       </c>
       <c r="BB21" s="3">
         <f t="shared" si="41"/>
-        <v>694.0893074528849</v>
+        <v>2255.7092208272993</v>
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="41"/>
-        <v>687.14841437835605</v>
+        <v>2233.1521286190264</v>
       </c>
       <c r="BD21" s="3">
         <f t="shared" si="41"/>
-        <v>680.27693023457243</v>
+        <v>2210.8206073328361</v>
       </c>
       <c r="BE21" s="3">
         <f t="shared" si="41"/>
-        <v>673.47416093222671</v>
+        <v>2188.7124012595077</v>
       </c>
       <c r="BF21" s="3">
         <f t="shared" si="41"/>
-        <v>666.73941932290438</v>
+        <v>2166.8252772469127</v>
       </c>
       <c r="BG21" s="3">
         <f t="shared" si="41"/>
-        <v>660.07202512967535</v>
+        <v>2145.1570244744435</v>
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="41"/>
-        <v>653.47130487837865</v>
+        <v>2123.7054542296992</v>
       </c>
       <c r="BI21" s="3">
         <f t="shared" si="41"/>
-        <v>646.93659182959482</v>
+        <v>2102.4683996874023</v>
       </c>
       <c r="BJ21" s="3">
         <f t="shared" si="41"/>
-        <v>640.4672259112989</v>
+        <v>2081.4437156905283</v>
       </c>
       <c r="BK21" s="3">
         <f t="shared" si="41"/>
-        <v>634.0625536521859</v>
+        <v>2060.6292785336232</v>
       </c>
       <c r="BL21" s="3">
         <f t="shared" si="41"/>
-        <v>627.72192811566401</v>
+        <v>2040.0229857482868</v>
       </c>
       <c r="BM21" s="3">
         <f t="shared" si="41"/>
-        <v>621.44470883450742</v>
+        <v>2019.622755890804</v>
       </c>
       <c r="BN21" s="3">
         <f t="shared" si="41"/>
-        <v>615.23026174616234</v>
+        <v>1999.426528331896</v>
       </c>
       <c r="BO21" s="3">
         <f t="shared" si="41"/>
-        <v>609.07795912870074</v>
+        <v>1979.4322630485769</v>
       </c>
       <c r="BP21" s="3">
         <f t="shared" si="41"/>
-        <v>602.98717953741368</v>
+        <v>1959.6379404180911</v>
       </c>
       <c r="BQ21" s="3">
         <f t="shared" si="41"/>
-        <v>596.95730774203957</v>
+        <v>1940.0415610139103</v>
       </c>
       <c r="BR21" s="3">
         <f t="shared" si="41"/>
-        <v>590.98773466461921</v>
+        <v>1920.6411454037711</v>
       </c>
       <c r="BS21" s="3">
         <f t="shared" si="41"/>
-        <v>585.07785731797298</v>
+        <v>1901.4347339497333</v>
       </c>
       <c r="BT21" s="3">
         <f t="shared" si="41"/>
-        <v>579.22707874479329</v>
+        <v>1882.4203866102359</v>
       </c>
       <c r="BU21" s="3">
         <f t="shared" si="41"/>
-        <v>573.43480795734536</v>
+        <v>1863.5961827441336</v>
       </c>
       <c r="BV21" s="3">
         <f t="shared" si="41"/>
-        <v>567.70045987777189</v>
+        <v>1844.9602209166922</v>
       </c>
       <c r="BW21" s="3">
         <f t="shared" si="41"/>
-        <v>562.02345527899422</v>
+        <v>1826.5106187075253</v>
       </c>
       <c r="BX21" s="3">
         <f t="shared" si="41"/>
-        <v>556.40322072620427</v>
+        <v>1808.2455125204501</v>
       </c>
       <c r="BY21" s="3">
         <f t="shared" si="41"/>
-        <v>550.83918851894225</v>
+        <v>1790.1630573952457</v>
       </c>
       <c r="BZ21" s="3">
         <f t="shared" si="41"/>
-        <v>545.33079663375281</v>
+        <v>1772.2614268212933</v>
       </c>
       <c r="CA21" s="3">
         <f t="shared" si="41"/>
-        <v>539.87748866741526</v>
+        <v>1754.5388125530803</v>
       </c>
       <c r="CB21" s="3">
         <f t="shared" si="41"/>
-        <v>534.47871378074115</v>
+        <v>1736.9934244275496</v>
       </c>
       <c r="CC21" s="3">
         <f t="shared" si="41"/>
-        <v>529.13392664293372</v>
+        <v>1719.623490183274</v>
       </c>
       <c r="CD21" s="3">
         <f t="shared" si="41"/>
-        <v>523.84258737650441</v>
+        <v>1702.4272552814414</v>
       </c>
       <c r="CE21" s="3">
         <f t="shared" si="41"/>
-        <v>518.60416150273932</v>
+        <v>1685.402982728627</v>
       </c>
       <c r="CF21" s="3">
         <f t="shared" si="41"/>
-        <v>513.4181198877119</v>
+        <v>1668.5489529013407</v>
       </c>
       <c r="CG21" s="3">
         <f t="shared" si="41"/>
-        <v>508.28393868883478</v>
+        <v>1651.8634633723273</v>
       </c>
       <c r="CH21" s="3">
         <f t="shared" si="41"/>
-        <v>503.20109930194644</v>
+        <v>1635.3448287386041</v>
       </c>
       <c r="CI21" s="3">
         <f t="shared" si="41"/>
-        <v>498.16908830892697</v>
+        <v>1618.991380451218</v>
       </c>
       <c r="CJ21" s="3">
         <f t="shared" si="41"/>
-        <v>493.18739742583767</v>
+        <v>1602.8014666467059</v>
       </c>
       <c r="CK21" s="3">
         <f t="shared" si="41"/>
-        <v>488.25552345157928</v>
+        <v>1586.7734519802389</v>
       </c>
       <c r="CL21" s="3">
         <f t="shared" si="41"/>
-        <v>483.37296821706349</v>
+        <v>1570.9057174604366</v>
       </c>
       <c r="CM21" s="3">
         <f t="shared" si="41"/>
-        <v>478.53923853489283</v>
+        <v>1555.1966602858322</v>
       </c>
       <c r="CN21" s="3">
         <f t="shared" si="41"/>
-        <v>473.7538461495439</v>
+        <v>1539.6446936829739</v>
       </c>
       <c r="CO21" s="3">
         <f t="shared" si="41"/>
-        <v>469.01630768804847</v>
+        <v>1524.2482467461441</v>
       </c>
       <c r="CP21" s="3">
         <f t="shared" si="41"/>
-        <v>464.32614461116799</v>
+        <v>1509.0057642786826</v>
       </c>
       <c r="CQ21" s="3">
         <f t="shared" si="41"/>
-        <v>459.6828831650563</v>
+        <v>1493.9157066358957</v>
       </c>
       <c r="CR21" s="3">
         <f t="shared" si="41"/>
-        <v>455.08605433340574</v>
+        <v>1478.9765495695367</v>
       </c>
       <c r="CS21" s="3">
         <f t="shared" si="41"/>
-        <v>450.53519379007167</v>
+        <v>1464.1867840738414</v>
       </c>
       <c r="CT21" s="3">
         <f t="shared" si="41"/>
-        <v>446.02984185217093</v>
+        <v>1449.5449162331031</v>
       </c>
       <c r="CU21" s="3">
         <f t="shared" si="41"/>
-        <v>441.56954343364924</v>
+        <v>1435.0494670707722</v>
       </c>
       <c r="CV21" s="3">
         <f t="shared" si="41"/>
-        <v>437.15384799931275</v>
+        <v>1420.6989724000643</v>
       </c>
       <c r="CW21" s="3">
         <f t="shared" si="41"/>
-        <v>432.7823095193196</v>
+        <v>1406.4919826760638</v>
       </c>
       <c r="CX21" s="3">
         <f t="shared" ref="CX21:EF21" si="42">CW21*(1+$AN$30)</f>
-        <v>428.4544864241264</v>
+        <v>1392.4270628493032</v>
       </c>
       <c r="CY21" s="3">
         <f t="shared" si="42"/>
-        <v>424.16994155988516</v>
+        <v>1378.5027922208101</v>
       </c>
       <c r="CZ21" s="3">
         <f t="shared" si="42"/>
-        <v>419.92824214428629</v>
+        <v>1364.7177642986019</v>
       </c>
       <c r="DA21" s="3">
         <f t="shared" si="42"/>
-        <v>415.7289597228434</v>
+        <v>1351.0705866556159</v>
       </c>
       <c r="DB21" s="3">
         <f t="shared" si="42"/>
-        <v>411.57167012561496</v>
+        <v>1337.5598807890597</v>
       </c>
       <c r="DC21" s="3">
         <f t="shared" si="42"/>
-        <v>407.45595342435882</v>
+        <v>1324.1842819811691</v>
       </c>
       <c r="DD21" s="3">
         <f t="shared" si="42"/>
-        <v>403.38139389011525</v>
+        <v>1310.9424391613575</v>
       </c>
       <c r="DE21" s="3">
         <f t="shared" si="42"/>
-        <v>399.34757995121407</v>
+        <v>1297.8330147697438</v>
       </c>
       <c r="DF21" s="3">
         <f t="shared" si="42"/>
-        <v>395.3541041517019</v>
+        <v>1284.8546846220463</v>
       </c>
       <c r="DG21" s="3">
         <f t="shared" si="42"/>
-        <v>391.40056311018486</v>
+        <v>1272.0061377758259</v>
       </c>
       <c r="DH21" s="3">
         <f t="shared" si="42"/>
-        <v>387.48655747908299</v>
+        <v>1259.2860763980677</v>
       </c>
       <c r="DI21" s="3">
         <f t="shared" si="42"/>
-        <v>383.61169190429217</v>
+        <v>1246.693215634087</v>
       </c>
       <c r="DJ21" s="3">
         <f t="shared" si="42"/>
-        <v>379.77557498524925</v>
+        <v>1234.2262834777462</v>
       </c>
       <c r="DK21" s="3">
         <f t="shared" si="42"/>
-        <v>375.97781923539674</v>
+        <v>1221.8840206429686</v>
       </c>
       <c r="DL21" s="3">
         <f t="shared" si="42"/>
-        <v>372.21804104304277</v>
+        <v>1209.665180436539</v>
       </c>
       <c r="DM21" s="3">
         <f t="shared" si="42"/>
-        <v>368.49586063261233</v>
+        <v>1197.5685286321736</v>
       </c>
       <c r="DN21" s="3">
         <f t="shared" si="42"/>
-        <v>364.81090202628621</v>
+        <v>1185.5928433458519</v>
       </c>
       <c r="DO21" s="3">
         <f t="shared" si="42"/>
-        <v>361.16279300602332</v>
+        <v>1173.7369149123933</v>
       </c>
       <c r="DP21" s="3">
         <f t="shared" si="42"/>
-        <v>357.55116507596307</v>
+        <v>1161.9995457632695</v>
       </c>
       <c r="DQ21" s="3">
         <f t="shared" si="42"/>
-        <v>353.97565342520346</v>
+        <v>1150.3795503056367</v>
       </c>
       <c r="DR21" s="3">
         <f t="shared" si="42"/>
-        <v>350.43589689095143</v>
+        <v>1138.8757548025803</v>
       </c>
       <c r="DS21" s="3">
         <f t="shared" si="42"/>
-        <v>346.93153792204191</v>
+        <v>1127.4869972545546</v>
       </c>
       <c r="DT21" s="3">
         <f t="shared" si="42"/>
-        <v>343.46222254282151</v>
+        <v>1116.2121272820091</v>
       </c>
       <c r="DU21" s="3">
         <f t="shared" si="42"/>
-        <v>340.02760031739331</v>
+        <v>1105.050006009189</v>
       </c>
       <c r="DV21" s="3">
         <f t="shared" si="42"/>
-        <v>336.62732431421938</v>
+        <v>1093.9995059490971</v>
       </c>
       <c r="DW21" s="3">
         <f t="shared" si="42"/>
-        <v>333.26105107107719</v>
+        <v>1083.0595108896061</v>
       </c>
       <c r="DX21" s="3">
         <f t="shared" si="42"/>
-        <v>329.92844056036643</v>
+        <v>1072.2289157807102</v>
       </c>
       <c r="DY21" s="3">
         <f t="shared" si="42"/>
-        <v>326.62915615476277</v>
+        <v>1061.506626622903</v>
       </c>
       <c r="DZ21" s="3">
         <f t="shared" si="42"/>
-        <v>323.36286459321514</v>
+        <v>1050.8915603566741</v>
       </c>
       <c r="EA21" s="3">
         <f t="shared" si="42"/>
-        <v>320.12923594728301</v>
+        <v>1040.3826447531073</v>
       </c>
       <c r="EB21" s="3">
         <f t="shared" si="42"/>
-        <v>316.92794358781015</v>
+        <v>1029.9788183055762</v>
       </c>
       <c r="EC21" s="3">
         <f t="shared" si="42"/>
-        <v>313.75866415193207</v>
+        <v>1019.6790301225204</v>
       </c>
       <c r="ED21" s="3">
         <f t="shared" si="42"/>
-        <v>310.62107751041276</v>
+        <v>1009.4822398212953</v>
       </c>
       <c r="EE21" s="3">
         <f t="shared" si="42"/>
-        <v>307.51486673530866</v>
+        <v>999.3874174230823</v>
       </c>
       <c r="EF21" s="3">
         <f t="shared" si="42"/>
-        <v>304.4397180679556</v>
+        <v>989.39354324885142</v>
       </c>
     </row>
     <row r="22" spans="2:136" x14ac:dyDescent="0.3">
@@ -3418,12 +3430,12 @@
         <v>1213.4000000000001</v>
       </c>
       <c r="Q22" s="6">
-        <f>1209.5+3.9</f>
-        <v>1213.4000000000001</v>
+        <f>1222+3.9</f>
+        <v>1225.9000000000001</v>
       </c>
       <c r="R22" s="6">
-        <f>1209.5+3.9</f>
-        <v>1213.4000000000001</v>
+        <f>1222+3.9</f>
+        <v>1225.9000000000001</v>
       </c>
       <c r="U22" s="6">
         <v>1058</v>
@@ -3441,48 +3453,48 @@
         <v>1058</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" ref="Z22:AJ22" si="43">1209.5+3.9</f>
-        <v>1213.4000000000001</v>
+        <f t="shared" ref="Z22:AJ22" si="43">1222+3.9</f>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AE22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AF22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AG22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AH22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AI22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
       <c r="AJ22" s="6">
         <f t="shared" si="43"/>
-        <v>1213.4000000000001</v>
+        <v>1225.9000000000001</v>
       </c>
     </row>
     <row r="23" spans="2:136" x14ac:dyDescent="0.3">
@@ -3531,11 +3543,11 @@
       </c>
       <c r="Q23" s="10">
         <f t="shared" ref="Q23" si="47">Q21/Q22</f>
-        <v>-0.51846876545244769</v>
+        <v>-0.95847948446039632</v>
       </c>
       <c r="R23" s="10">
         <f t="shared" ref="R23" si="48">R21/R22</f>
-        <v>-0.48792615790341193</v>
+        <v>-0.50900562851782361</v>
       </c>
       <c r="U23" s="10">
         <f t="shared" ref="U23:AA23" si="49">U21/U22</f>
@@ -3559,47 +3571,47 @@
       </c>
       <c r="Z23" s="10">
         <f t="shared" si="49"/>
-        <v>-2.3760998846217238</v>
+        <v>-2.8232237539766705</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" si="49"/>
-        <v>-1.7941003692104822</v>
+        <v>-2.1073349375968675</v>
       </c>
       <c r="AB23" s="10">
         <f t="shared" ref="AB23:AJ23" si="50">AB21/AB22</f>
-        <v>-1.2518275745904073</v>
+        <v>-1.3315480420915251</v>
       </c>
       <c r="AC23" s="10">
         <f t="shared" si="50"/>
-        <v>-1.0516843397907365</v>
+        <v>-0.9716279575756589</v>
       </c>
       <c r="AD23" s="10">
         <f t="shared" si="50"/>
-        <v>-0.84352492390820943</v>
+        <v>-0.60743569961680377</v>
       </c>
       <c r="AE23" s="10">
         <f t="shared" si="50"/>
-        <v>-0.6200772977590554</v>
+        <v>-0.22124170745174263</v>
       </c>
       <c r="AF23" s="10">
         <f t="shared" si="50"/>
-        <v>-0.35382791635211247</v>
+        <v>0.21175169985007447</v>
       </c>
       <c r="AG23" s="10">
         <f t="shared" si="50"/>
-        <v>-0.12289314489246922</v>
+        <v>0.63020172864317858</v>
       </c>
       <c r="AH23" s="10">
         <f t="shared" si="50"/>
-        <v>0.14188969188991182</v>
+        <v>1.1149769733795711</v>
       </c>
       <c r="AI23" s="10">
         <f t="shared" si="50"/>
-        <v>0.44541214796312628</v>
+        <v>1.6760497290035488</v>
       </c>
       <c r="AJ23" s="10">
         <f t="shared" si="50"/>
-        <v>0.68545328281521523</v>
+        <v>2.2049287844938625</v>
       </c>
     </row>
     <row r="25" spans="2:136" x14ac:dyDescent="0.3">
@@ -3618,16 +3630,20 @@
         <f t="shared" ref="P25:P26" si="52">P3/L3-1</f>
         <v>-0.13687150837988826</v>
       </c>
-      <c r="Q25" s="12" t="e">
+      <c r="Q25" s="12">
         <f t="shared" ref="Q25:Q26" si="53">Q3/M3-1</f>
-        <v>#DIV/0!</v>
+        <v>0.47164948453608257</v>
       </c>
       <c r="R25" s="12">
         <f t="shared" ref="R25:R26" si="54">R3/N3-1</f>
-        <v>-1.3157894736842146E-2</v>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="Z25" s="12">
+        <f t="shared" ref="Z25:AJ27" si="55">Z3/Y3-1</f>
+        <v>3.9456085599643309E-2</v>
       </c>
       <c r="AA25" s="12">
-        <f t="shared" ref="Z25:AJ27" si="55">AA3/Z3-1</f>
+        <f t="shared" si="55"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AB25" s="12">
@@ -3683,13 +3699,17 @@
         <f t="shared" si="52"/>
         <v>3.4761904761904763</v>
       </c>
-      <c r="Q26" s="12" t="e">
+      <c r="Q26" s="12">
         <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
+        <v>3.2448979591836737</v>
       </c>
       <c r="R26" s="12">
         <f t="shared" si="54"/>
-        <v>0.96261682242990654</v>
+        <v>1.5</v>
+      </c>
+      <c r="Z26" s="12">
+        <f t="shared" si="55"/>
+        <v>2.3987603305785123</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="55"/>
@@ -3705,31 +3725,31 @@
       </c>
       <c r="AD26" s="12">
         <f t="shared" si="58"/>
-        <v>0.10000000000000009</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AE26" s="12">
         <f t="shared" si="59"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="60"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AG26" s="12">
         <f t="shared" si="61"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AH26" s="12">
         <f t="shared" si="62"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AI26" s="12">
         <f t="shared" si="63"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AJ26" s="12">
         <f t="shared" si="64"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.14999999999999991</v>
       </c>
     </row>
     <row r="27" spans="2:136" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3766,11 +3786,11 @@
       </c>
       <c r="Q27" s="11">
         <f t="shared" si="51"/>
-        <v>0.28146453089244861</v>
+        <v>0.78260869565217384</v>
       </c>
       <c r="R27" s="11">
         <f t="shared" si="51"/>
-        <v>0.10726643598615926</v>
+        <v>0.27277970011534025</v>
       </c>
       <c r="T27" s="11"/>
       <c r="U27" s="11"/>
@@ -3789,15 +3809,15 @@
       </c>
       <c r="Z27" s="11">
         <f t="shared" si="55"/>
-        <v>0.12334004024144862</v>
+        <v>0.26921529175050307</v>
       </c>
       <c r="AA27" s="11">
         <f t="shared" si="55"/>
-        <v>0.30000000000000004</v>
+        <v>0.30000000000000027</v>
       </c>
       <c r="AB27" s="11">
         <f t="shared" si="55"/>
-        <v>0.19999999999999996</v>
+        <v>0.19999999999999973</v>
       </c>
       <c r="AC27" s="11">
         <f t="shared" si="55"/>
@@ -3805,31 +3825,31 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="55"/>
-        <v>0.1371574422353572</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AE27" s="11">
         <f t="shared" si="55"/>
-        <v>0.12515416420555225</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AF27" s="11">
         <f t="shared" si="55"/>
-        <v>0.12681373058545242</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AG27" s="11">
         <f t="shared" si="55"/>
-        <v>0.12839431467290852</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AH27" s="11">
         <f t="shared" si="55"/>
-        <v>0.12989535280490849</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="55"/>
-        <v>0.13131696045793806</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AJ27" s="11">
         <f t="shared" si="55"/>
-        <v>9.1329931308011147E-2</v>
+        <v>0.11303899809765383</v>
       </c>
     </row>
     <row r="28" spans="2:136" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3863,11 +3883,11 @@
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="67"/>
-        <v>0.13</v>
+        <v>-0.11383537653239929</v>
       </c>
       <c r="R28" s="12">
         <f t="shared" si="67"/>
-        <v>0.12</v>
+        <v>0.12000000000000004</v>
       </c>
       <c r="T28" s="11"/>
       <c r="U28" s="11"/>
@@ -3877,47 +3897,47 @@
       <c r="Y28" s="11"/>
       <c r="Z28" s="12">
         <f t="shared" ref="Z28:AJ28" si="68">(Z3-Z6)/Z3</f>
-        <v>9.8818992528320083E-3</v>
+        <v>-3.6963328329401794E-2</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="68"/>
-        <v>0.14000000000000007</v>
+        <v>8.0000000000000029E-2</v>
       </c>
       <c r="AB28" s="12">
         <f t="shared" si="68"/>
-        <v>0.15</v>
+        <v>0.11999999999999997</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="68"/>
-        <v>0.16000000000000006</v>
+        <v>0.15000000000000008</v>
       </c>
       <c r="AD28" s="12">
         <f t="shared" si="68"/>
-        <v>0.17000000000000007</v>
+        <v>0.1700000000000001</v>
       </c>
       <c r="AE28" s="12">
         <f t="shared" si="68"/>
-        <v>0.18000000000000002</v>
+        <v>0.18000000000000008</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="68"/>
-        <v>0.18999999999999995</v>
+        <v>0.18999999999999992</v>
       </c>
       <c r="AG28" s="12">
         <f t="shared" si="68"/>
-        <v>0.18999999999999995</v>
+        <v>0.18999999999999992</v>
       </c>
       <c r="AH28" s="12">
         <f t="shared" si="68"/>
-        <v>0.18999999999999989</v>
+        <v>0.19</v>
       </c>
       <c r="AI28" s="12">
         <f t="shared" si="68"/>
-        <v>0.18999999999999997</v>
+        <v>0.19</v>
       </c>
       <c r="AJ28" s="12">
         <f t="shared" si="68"/>
-        <v>0.19</v>
+        <v>0.18999999999999995</v>
       </c>
     </row>
     <row r="29" spans="2:136" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3951,7 +3971,7 @@
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="69"/>
-        <v>0.4</v>
+        <v>0.37019230769230771</v>
       </c>
       <c r="R29" s="12">
         <f t="shared" si="69"/>
@@ -3965,7 +3985,7 @@
       <c r="Y29" s="11"/>
       <c r="Z29" s="12">
         <f t="shared" ref="Z29:AJ29" si="70">(Z4-Z7)/Z4</f>
-        <v>0.37587168758716877</v>
+        <v>0.37142857142857144</v>
       </c>
       <c r="AA29" s="12">
         <f t="shared" si="70"/>
@@ -3973,39 +3993,39 @@
       </c>
       <c r="AB29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.4300000000000001</v>
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AE29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="70"/>
-        <v>0.40000000000000008</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="AG29" s="12">
         <f t="shared" si="70"/>
-        <v>0.40000000000000008</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="AH29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="AI29" s="12">
         <f t="shared" si="70"/>
-        <v>0.39999999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="AJ29" s="12">
         <f t="shared" si="70"/>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="30" spans="2:136" x14ac:dyDescent="0.3">
@@ -4054,11 +4074,11 @@
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="72"/>
-        <v>0.20714285714285716</v>
+        <v>1.540436456996149E-2</v>
       </c>
       <c r="R30" s="12">
         <f t="shared" si="72"/>
-        <v>0.18124999999999999</v>
+        <v>0.18787494336202984</v>
       </c>
       <c r="T30" s="12"/>
       <c r="U30" s="12"/>
@@ -4080,47 +4100,47 @@
       </c>
       <c r="Z30" s="12">
         <f t="shared" ref="Z30:AJ30" si="74">Z9/Z5</f>
-        <v>0.10388679921189324</v>
+        <v>6.9537095751426664E-2</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="74"/>
-        <v>0.20678130037614195</v>
+        <v>0.1634495878249842</v>
       </c>
       <c r="AB30" s="12">
         <f t="shared" si="74"/>
-        <v>0.21421278882321332</v>
+        <v>0.20084178820545334</v>
       </c>
       <c r="AC30" s="12">
         <f t="shared" si="74"/>
-        <v>0.22164427727028488</v>
+        <v>0.22823398858592261</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="74"/>
-        <v>0.22714542232722981</v>
+        <v>0.24562618896639193</v>
       </c>
       <c r="AE30" s="12">
         <f t="shared" si="74"/>
-        <v>0.23100979271200475</v>
+        <v>0.255626188966392</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="74"/>
-        <v>0.23537193918689153</v>
+        <v>0.26301838934686106</v>
       </c>
       <c r="AG30" s="12">
         <f t="shared" si="74"/>
-        <v>0.23221975910969186</v>
+        <v>0.26301838934686106</v>
       </c>
       <c r="AH30" s="12">
         <f t="shared" si="74"/>
-        <v>0.22923438303832977</v>
+        <v>0.26301838934686111</v>
       </c>
       <c r="AI30" s="12">
         <f t="shared" si="74"/>
-        <v>0.22641428850635353</v>
+        <v>0.26301838934686111</v>
       </c>
       <c r="AJ30" s="12">
         <f t="shared" si="74"/>
-        <v>0.22503523713112558</v>
+        <v>0.26544313172531164</v>
       </c>
       <c r="AM30" s="1" t="s">
         <v>53</v>
@@ -4163,11 +4183,11 @@
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="76"/>
-        <v>5.428571428571427E-2</v>
+        <v>0.29428571428571426</v>
       </c>
       <c r="R31" s="12">
         <f t="shared" si="76"/>
-        <v>0.15106951871657759</v>
+        <v>0.26069518716577522</v>
       </c>
       <c r="T31" s="12"/>
       <c r="U31" s="12"/>
@@ -4189,7 +4209,7 @@
       </c>
       <c r="Z31" s="12">
         <f t="shared" ref="Z31:AJ31" si="78">Z10/Y10-1</f>
-        <v>-1.3949163050216984E-2</v>
+        <v>6.3546187228766371E-2</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="78"/>
@@ -4284,11 +4304,11 @@
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="80"/>
-        <v>0.45353571428571432</v>
+        <v>0.35558408215661103</v>
       </c>
       <c r="R32" s="12">
         <f t="shared" si="80"/>
-        <v>0.26720812500000002</v>
+        <v>0.25855006796556412</v>
       </c>
       <c r="T32" s="12"/>
       <c r="U32" s="12"/>
@@ -4310,54 +4330,54 @@
       </c>
       <c r="Z32" s="12">
         <f t="shared" ref="Z32:AJ32" si="82">Z11/Z5</f>
-        <v>0.35805115529285331</v>
+        <v>0.33332593532022825</v>
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="82"/>
-        <v>0.2836866845781838</v>
+        <v>0.26409670259987317</v>
       </c>
       <c r="AB32" s="12">
         <f t="shared" si="82"/>
-        <v>0.2411336818914562</v>
+        <v>0.22448219720989221</v>
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="82"/>
-        <v>0.21177827713945288</v>
+        <v>0.19715392972347054</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="82"/>
-        <v>0.18809713762272276</v>
+        <v>0.17315258175713499</v>
       </c>
       <c r="AE32" s="12">
         <f t="shared" si="82"/>
-        <v>0.16884629239504217</v>
+        <v>0.15207313702148378</v>
       </c>
       <c r="AF32" s="12">
         <f t="shared" si="82"/>
-        <v>0.15134245411651917</v>
+        <v>0.1335598855579988</v>
       </c>
       <c r="AG32" s="12">
         <f t="shared" si="82"/>
-        <v>0.13546317689662696</v>
+        <v>0.11730042122919898</v>
       </c>
       <c r="AH32" s="12">
         <f t="shared" si="82"/>
-        <v>0.12108892060308937</v>
+        <v>0.10302036994912261</v>
       </c>
       <c r="AI32" s="12">
         <f t="shared" si="82"/>
-        <v>0.10810393027221597</v>
+        <v>9.0478759694446811E-2</v>
       </c>
       <c r="AJ32" s="12">
         <f t="shared" si="82"/>
-        <v>0.10004762670082247</v>
+        <v>8.2102736245162219E-2</v>
       </c>
       <c r="AM32" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AN32" s="6">
         <f>NPV(AN31,Z21:EF21)</f>
-        <v>-4157.2447534596513</v>
+        <v>5344.564445321741</v>
       </c>
     </row>
     <row r="33" spans="2:40" x14ac:dyDescent="0.3">
@@ -4406,11 +4426,11 @@
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="84"/>
-        <v>-0.57585714285714285</v>
+        <v>-0.63093709884467264</v>
       </c>
       <c r="R33" s="12">
         <f t="shared" si="84"/>
-        <v>-0.31017687500000002</v>
+        <v>-0.28431354780244678</v>
       </c>
       <c r="T33" s="12"/>
       <c r="U33" s="12"/>
@@ -4432,54 +4452,54 @@
       </c>
       <c r="Z33" s="12">
         <f t="shared" ref="Z33:AJ33" si="86">Z12/Z5</f>
-        <v>-0.53904703564391909</v>
+        <v>-0.53574508560558032</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="86"/>
-        <v>-0.304811527852409</v>
+        <v>-0.3182121116043119</v>
       </c>
       <c r="AB33" s="12">
         <f t="shared" si="86"/>
-        <v>-0.22254033303480808</v>
+        <v>-0.21038369794969358</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="86"/>
-        <v>-0.16363993792646933</v>
+        <v>-0.13455311915855644</v>
       </c>
       <c r="AD33" s="12">
         <f t="shared" si="86"/>
-        <v>-0.11658192993890966</v>
+        <v>-7.4435820252855001E-2</v>
       </c>
       <c r="AE33" s="12">
         <f t="shared" si="86"/>
-        <v>-7.7538703870173808E-2</v>
+        <v>-2.5471749565294469E-2</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="86"/>
-        <v>-4.1190169606445989E-2</v>
+        <v>1.6141069419032105E-2</v>
       </c>
       <c r="AG33" s="12">
         <f t="shared" si="86"/>
-        <v>-1.5324673052960907E-2</v>
+        <v>4.6195699671115552E-2</v>
       </c>
       <c r="AH33" s="12">
         <f t="shared" si="86"/>
-        <v>7.9573631235053573E-3</v>
+        <v>7.2591505370771567E-2</v>
       </c>
       <c r="AI33" s="12">
         <f t="shared" si="86"/>
-        <v>2.8865946242035558E-2</v>
+        <v>9.5773908637425936E-2</v>
       </c>
       <c r="AJ33" s="12">
         <f t="shared" si="86"/>
-        <v>4.2208925891020294E-2</v>
+        <v>0.11368122059260811</v>
       </c>
       <c r="AM33" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AN33" s="6">
         <f>Main!D8</f>
-        <v>3259</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="34" spans="2:40" x14ac:dyDescent="0.3">
@@ -4528,7 +4548,7 @@
       </c>
       <c r="Q34" s="12">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>-8.5689802913453304E-4</v>
       </c>
       <c r="R34" s="12">
         <f t="shared" si="88"/>
@@ -4554,7 +4574,7 @@
       </c>
       <c r="Z34" s="12">
         <f t="shared" ref="Z34:AJ34" si="90">Z19/Z18</f>
-        <v>-1.3921955466727292E-3</v>
+        <v>-1.4522261174153858E-3</v>
       </c>
       <c r="AA34" s="12">
         <f t="shared" si="90"/>
@@ -4566,7 +4586,7 @@
       </c>
       <c r="AC34" s="12">
         <f t="shared" si="90"/>
-        <v>0.20000000000000004</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="90"/>
@@ -4582,7 +4602,7 @@
       </c>
       <c r="AG34" s="12">
         <f t="shared" si="90"/>
-        <v>0.19999999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="AH34" s="12">
         <f t="shared" si="90"/>
@@ -4590,7 +4610,7 @@
       </c>
       <c r="AI34" s="12">
         <f t="shared" si="90"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AJ34" s="12">
         <f t="shared" si="90"/>
@@ -4601,7 +4621,7 @@
       </c>
       <c r="AN34" s="6">
         <f>AN32+AN33</f>
-        <v>-898.24475345965129</v>
+        <v>7994.564445321741</v>
       </c>
     </row>
     <row r="35" spans="2:40" x14ac:dyDescent="0.3">
@@ -4650,11 +4670,11 @@
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="92"/>
-        <v>-0.56170535714285719</v>
+        <v>-0.75417201540436452</v>
       </c>
       <c r="R35" s="12">
         <f t="shared" si="92"/>
-        <v>-0.30835916666666668</v>
+        <v>-0.28273221567739015</v>
       </c>
       <c r="T35" s="12"/>
       <c r="U35" s="12"/>
@@ -4676,54 +4696,54 @@
       </c>
       <c r="Z35" s="12">
         <f t="shared" ref="Z35:AJ35" si="94">Z21/Z5</f>
-        <v>-0.51641762493283183</v>
+        <v>-0.54866677235256822</v>
       </c>
       <c r="AA35" s="12">
         <f t="shared" si="94"/>
-        <v>-0.29994370107055751</v>
+        <v>-0.31503120579483923</v>
       </c>
       <c r="AB35" s="12">
         <f t="shared" si="94"/>
-        <v>-0.17440393444935867</v>
+        <v>-0.16588060184056069</v>
       </c>
       <c r="AC35" s="12">
         <f t="shared" si="94"/>
-        <v>-0.12740877236040049</v>
+        <v>-0.10525456103519874</v>
       </c>
       <c r="AD35" s="12">
         <f t="shared" si="94"/>
-        <v>-8.9865137970147183E-2</v>
+        <v>-5.721941239624162E-2</v>
       </c>
       <c r="AE35" s="12">
         <f t="shared" si="94"/>
-        <v>-5.8712033904367564E-2</v>
+        <v>-1.8122255224302743E-2</v>
       </c>
       <c r="AF35" s="12">
         <f t="shared" si="94"/>
-        <v>-2.9731803837984117E-2</v>
+        <v>1.5082533755432514E-2</v>
       </c>
       <c r="AG35" s="12">
         <f t="shared" si="94"/>
-        <v>-9.1515768847995373E-3</v>
+        <v>3.9032750034171358E-2</v>
       </c>
       <c r="AH35" s="12">
         <f t="shared" si="94"/>
-        <v>9.3514918080394374E-3</v>
+        <v>6.0050636952712337E-2</v>
       </c>
       <c r="AI35" s="12">
         <f t="shared" si="94"/>
-        <v>2.5948234356200337E-2</v>
+        <v>7.8494780566215172E-2</v>
       </c>
       <c r="AJ35" s="12">
         <f t="shared" si="94"/>
-        <v>3.6590432953878975E-2</v>
+        <v>9.2776517241754675E-2</v>
       </c>
       <c r="AM35" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AN35" s="4">
         <f>AN34/AJ22</f>
-        <v>-0.74027093576697811</v>
+        <v>6.5213838366275718</v>
       </c>
     </row>
     <row r="36" spans="2:40" x14ac:dyDescent="0.3">
@@ -4732,7 +4752,7 @@
       </c>
       <c r="AN36" s="4">
         <f>Main!D3</f>
-        <v>12.68</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="37" spans="2:40" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -4752,7 +4772,7 @@
       </c>
       <c r="AN37" s="11">
         <f>AN35/AN36-1</f>
-        <v>-1.0583809886251561</v>
+        <v>-0.60113860326436874</v>
       </c>
     </row>
     <row r="38" spans="2:40" x14ac:dyDescent="0.3">
@@ -5018,47 +5038,47 @@
       </c>
       <c r="Z60" s="9">
         <f t="shared" ref="Z60:AJ60" si="95">Z21</f>
-        <v>-2883.1596</v>
+        <v>-3460.9900000000007</v>
       </c>
       <c r="AA60" s="9">
         <f t="shared" si="95"/>
-        <v>-2176.9613879999993</v>
+        <v>-2583.3818999999999</v>
       </c>
       <c r="AB60" s="9">
         <f t="shared" si="95"/>
-        <v>-1518.9675790080003</v>
+        <v>-1632.3447448000006</v>
       </c>
       <c r="AC60" s="9">
         <f t="shared" si="95"/>
-        <v>-1276.1137779020798</v>
+        <v>-1191.1187131920003</v>
       </c>
       <c r="AD60" s="9">
         <f t="shared" si="95"/>
-        <v>-1023.5331426702214</v>
+        <v>-744.65542416023982</v>
       </c>
       <c r="AE60" s="9">
         <f t="shared" si="95"/>
-        <v>-752.40179310083784</v>
+        <v>-271.22020916509132</v>
       </c>
       <c r="AF60" s="9">
         <f t="shared" si="95"/>
-        <v>-429.33479370165333</v>
+        <v>259.58640884620633</v>
       </c>
       <c r="AG60" s="9">
         <f t="shared" si="95"/>
-        <v>-149.11854201252217</v>
+        <v>772.56429914367266</v>
       </c>
       <c r="AH60" s="9">
         <f t="shared" si="95"/>
-        <v>172.16895213921902</v>
+        <v>1366.8502716660164</v>
       </c>
       <c r="AI60" s="9">
         <f t="shared" si="95"/>
-        <v>540.46310033845748</v>
+        <v>2054.6693627854506</v>
       </c>
       <c r="AJ60" s="9">
         <f t="shared" si="95"/>
-        <v>831.72901336798225</v>
+        <v>2703.0221969110262</v>
       </c>
     </row>
     <row r="61" spans="2:36" x14ac:dyDescent="0.3">
@@ -5591,47 +5611,47 @@
       </c>
       <c r="Z72" s="9">
         <f t="shared" ref="Z72:AJ72" si="100">Z60+SUM(Z61:Z71)</f>
-        <v>-1181.4796000000001</v>
+        <v>-1759.3100000000009</v>
       </c>
       <c r="AA72" s="9">
         <f t="shared" si="100"/>
-        <v>-474.43298799999911</v>
+        <v>-880.85349999999971</v>
       </c>
       <c r="AB72" s="9">
         <f t="shared" si="100"/>
-        <v>192.74440899199976</v>
+        <v>79.367243199999393</v>
       </c>
       <c r="AC72" s="9">
         <f t="shared" si="100"/>
-        <v>449.05628437792052</v>
+        <v>534.05134908800005</v>
       </c>
       <c r="AD72" s="9">
         <f t="shared" si="100"/>
-        <v>715.64975772377898</v>
+        <v>994.52747623376058</v>
       </c>
       <c r="AE72" s="9">
         <f t="shared" si="100"/>
-        <v>998.0100488214224</v>
+        <v>1479.1916327571689</v>
       </c>
       <c r="AF72" s="9">
         <f t="shared" si="100"/>
-        <v>1326.6116598120248</v>
+        <v>2015.5328623598843</v>
       </c>
       <c r="AG72" s="9">
         <f t="shared" si="100"/>
-        <v>1604.2341519060233</v>
+        <v>2525.9169930622179</v>
       </c>
       <c r="AH72" s="9">
         <f t="shared" si="100"/>
-        <v>1928.53291457054</v>
+        <v>3123.2142340973373</v>
       </c>
       <c r="AI72" s="9">
         <f t="shared" si="100"/>
-        <v>2304.7069244576487</v>
+        <v>3818.9131869046423</v>
       </c>
       <c r="AJ72" s="9">
         <f t="shared" si="100"/>
-        <v>2608.0974090429149</v>
+        <v>4479.390592585959</v>
       </c>
     </row>
     <row r="73" spans="2:140" x14ac:dyDescent="0.3">
@@ -5703,499 +5723,504 @@
       </c>
       <c r="Z74" s="9">
         <f t="shared" ref="Z74:AJ74" si="102">Z72-Z73</f>
-        <v>-2379.5295999999998</v>
+        <v>-2957.3600000000006</v>
       </c>
       <c r="AA74" s="9">
         <f t="shared" si="102"/>
-        <v>-1708.4244879999992</v>
+        <v>-2114.8449999999998</v>
       </c>
       <c r="AB74" s="9">
         <f t="shared" si="102"/>
-        <v>-1065.9269210080004</v>
+        <v>-1179.3040868000007</v>
       </c>
       <c r="AC74" s="9">
         <f t="shared" si="102"/>
-        <v>-822.20175892207953</v>
+        <v>-737.206694212</v>
       </c>
       <c r="AD74" s="9">
         <f t="shared" si="102"/>
-        <v>-568.32086600922116</v>
+        <v>-289.44314749923956</v>
       </c>
       <c r="AE74" s="9">
         <f t="shared" si="102"/>
-        <v>-298.80028114890786</v>
+        <v>182.38130278683866</v>
       </c>
       <c r="AF74" s="9">
         <f t="shared" si="102"/>
-        <v>16.83322654199128</v>
+        <v>705.75442908985087</v>
       </c>
       <c r="AG74" s="9">
         <f t="shared" si="102"/>
-        <v>281.35793430328954</v>
+        <v>1203.0407754594842</v>
       </c>
       <c r="AH74" s="9">
         <f t="shared" si="102"/>
-        <v>592.42793479177885</v>
+        <v>1787.1092543185762</v>
       </c>
       <c r="AI74" s="9">
         <f t="shared" si="102"/>
-        <v>955.24089488109985</v>
+        <v>2469.4471573280935</v>
       </c>
       <c r="AJ74" s="9">
         <f t="shared" si="102"/>
-        <v>1245.1367191706006</v>
+        <v>3116.4299027136449</v>
       </c>
       <c r="AK74" s="3">
         <f>AJ74*(1+$AN$30)</f>
-        <v>1232.6853519788947</v>
+        <v>3085.2656036865083</v>
       </c>
       <c r="AL74" s="3">
         <f t="shared" ref="AL74:CW74" si="103">AK74*(1+$AN$30)</f>
-        <v>1220.3584984591057</v>
+        <v>3054.4129476496432</v>
       </c>
       <c r="AM74" s="3">
         <f t="shared" si="103"/>
-        <v>1208.1549134745146</v>
+        <v>3023.8688181731468</v>
       </c>
       <c r="AN74" s="3">
         <f t="shared" si="103"/>
-        <v>1196.0733643397696</v>
+        <v>2993.6301299914153</v>
       </c>
       <c r="AO74" s="3">
         <f t="shared" si="103"/>
-        <v>1184.1126306963718</v>
+        <v>2963.693828691501</v>
       </c>
       <c r="AP74" s="3">
         <f t="shared" si="103"/>
-        <v>1172.2715043894079</v>
+        <v>2934.0568904045858</v>
       </c>
       <c r="AQ74" s="3">
         <f t="shared" si="103"/>
-        <v>1160.5487893455138</v>
+        <v>2904.7163215005398</v>
       </c>
       <c r="AR74" s="3">
         <f t="shared" si="103"/>
-        <v>1148.9433014520587</v>
+        <v>2875.6691582855342</v>
       </c>
       <c r="AS74" s="3">
         <f t="shared" si="103"/>
-        <v>1137.4538684375382</v>
+        <v>2846.912466702679</v>
       </c>
       <c r="AT74" s="3">
         <f t="shared" si="103"/>
-        <v>1126.0793297531627</v>
+        <v>2818.4433420356522</v>
       </c>
       <c r="AU74" s="3">
         <f t="shared" si="103"/>
-        <v>1114.8185364556311</v>
+        <v>2790.2589086152957</v>
       </c>
       <c r="AV74" s="3">
         <f t="shared" si="103"/>
-        <v>1103.6703510910747</v>
+        <v>2762.3563195291426</v>
       </c>
       <c r="AW74" s="3">
         <f t="shared" si="103"/>
-        <v>1092.6336475801641</v>
+        <v>2734.7327563338513</v>
       </c>
       <c r="AX74" s="3">
         <f t="shared" si="103"/>
-        <v>1081.7073111043624</v>
+        <v>2707.3854287705126</v>
       </c>
       <c r="AY74" s="3">
         <f t="shared" si="103"/>
-        <v>1070.8902379933188</v>
+        <v>2680.3115744828074</v>
       </c>
       <c r="AZ74" s="3">
         <f t="shared" si="103"/>
-        <v>1060.1813356133855</v>
+        <v>2653.5084587379793</v>
       </c>
       <c r="BA74" s="3">
         <f t="shared" si="103"/>
-        <v>1049.5795222572517</v>
+        <v>2626.9733741505993</v>
       </c>
       <c r="BB74" s="3">
         <f t="shared" si="103"/>
-        <v>1039.0837270346792</v>
+        <v>2600.7036404090932</v>
       </c>
       <c r="BC74" s="3">
         <f t="shared" si="103"/>
-        <v>1028.6928897643324</v>
+        <v>2574.6966040050024</v>
       </c>
       <c r="BD74" s="3">
         <f t="shared" si="103"/>
-        <v>1018.4059608666892</v>
+        <v>2548.9496379649522</v>
       </c>
       <c r="BE74" s="3">
         <f t="shared" si="103"/>
-        <v>1008.2219012580223</v>
+        <v>2523.4601415853026</v>
       </c>
       <c r="BF74" s="3">
         <f t="shared" si="103"/>
-        <v>998.13968224544203</v>
+        <v>2498.2255401694497</v>
       </c>
       <c r="BG74" s="3">
         <f t="shared" si="103"/>
-        <v>988.15828542298755</v>
+        <v>2473.2432847677551</v>
       </c>
       <c r="BH74" s="3">
         <f t="shared" si="103"/>
-        <v>978.27670256875763</v>
+        <v>2448.5108519200776</v>
       </c>
       <c r="BI74" s="3">
         <f t="shared" si="103"/>
-        <v>968.49393554307005</v>
+        <v>2424.0257434008768</v>
       </c>
       <c r="BJ74" s="3">
         <f t="shared" si="103"/>
-        <v>958.80899618763931</v>
+        <v>2399.7854859668678</v>
       </c>
       <c r="BK74" s="3">
         <f t="shared" si="103"/>
-        <v>949.22090622576286</v>
+        <v>2375.7876311071991</v>
       </c>
       <c r="BL74" s="3">
         <f t="shared" si="103"/>
-        <v>939.72869716350522</v>
+        <v>2352.0297547961272</v>
       </c>
       <c r="BM74" s="3">
         <f t="shared" si="103"/>
-        <v>930.33141019187019</v>
+        <v>2328.5094572481657</v>
       </c>
       <c r="BN74" s="3">
         <f t="shared" si="103"/>
-        <v>921.02809608995153</v>
+        <v>2305.224362675684</v>
       </c>
       <c r="BO74" s="3">
         <f t="shared" si="103"/>
-        <v>911.81781512905206</v>
+        <v>2282.172119048927</v>
       </c>
       <c r="BP74" s="3">
         <f t="shared" si="103"/>
-        <v>902.69963697776154</v>
+        <v>2259.3503978584376</v>
       </c>
       <c r="BQ74" s="3">
         <f t="shared" si="103"/>
-        <v>893.67264060798391</v>
+        <v>2236.7568938798531</v>
       </c>
       <c r="BR74" s="3">
         <f t="shared" si="103"/>
-        <v>884.73591420190405</v>
+        <v>2214.3893249410544</v>
       </c>
       <c r="BS74" s="3">
         <f t="shared" si="103"/>
-        <v>875.88855505988499</v>
+        <v>2192.2454316916437</v>
       </c>
       <c r="BT74" s="3">
         <f t="shared" si="103"/>
-        <v>867.12966950928615</v>
+        <v>2170.3229773747271</v>
       </c>
       <c r="BU74" s="3">
         <f t="shared" si="103"/>
-        <v>858.45837281419324</v>
+        <v>2148.6197476009797</v>
       </c>
       <c r="BV74" s="3">
         <f t="shared" si="103"/>
-        <v>849.87378908605126</v>
+        <v>2127.13355012497</v>
       </c>
       <c r="BW74" s="3">
         <f t="shared" si="103"/>
-        <v>841.37505119519074</v>
+        <v>2105.8622146237203</v>
       </c>
       <c r="BX74" s="3">
         <f t="shared" si="103"/>
-        <v>832.96130068323885</v>
+        <v>2084.8035924774831</v>
       </c>
       <c r="BY74" s="3">
         <f t="shared" si="103"/>
-        <v>824.6316876764065</v>
+        <v>2063.9555565527085</v>
       </c>
       <c r="BZ74" s="3">
         <f t="shared" si="103"/>
-        <v>816.38537079964237</v>
+        <v>2043.3160009871813</v>
       </c>
       <c r="CA74" s="3">
         <f t="shared" si="103"/>
-        <v>808.22151709164598</v>
+        <v>2022.8828409773093</v>
       </c>
       <c r="CB74" s="3">
         <f t="shared" si="103"/>
-        <v>800.13930192072951</v>
+        <v>2002.6540125675363</v>
       </c>
       <c r="CC74" s="3">
         <f t="shared" si="103"/>
-        <v>792.13790890152222</v>
+        <v>1982.6274724418608</v>
       </c>
       <c r="CD74" s="3">
         <f t="shared" si="103"/>
-        <v>784.21652981250702</v>
+        <v>1962.8011977174422</v>
       </c>
       <c r="CE74" s="3">
         <f t="shared" si="103"/>
-        <v>776.37436451438191</v>
+        <v>1943.1731857402676</v>
       </c>
       <c r="CF74" s="3">
         <f t="shared" si="103"/>
-        <v>768.61062086923812</v>
+        <v>1923.741453882865</v>
       </c>
       <c r="CG74" s="3">
         <f t="shared" si="103"/>
-        <v>760.9245146605457</v>
+        <v>1904.5040393440363</v>
       </c>
       <c r="CH74" s="3">
         <f t="shared" si="103"/>
-        <v>753.31526951394028</v>
+        <v>1885.458998950596</v>
       </c>
       <c r="CI74" s="3">
         <f t="shared" si="103"/>
-        <v>745.78211681880089</v>
+        <v>1866.60440896109</v>
       </c>
       <c r="CJ74" s="3">
         <f t="shared" si="103"/>
-        <v>738.32429565061284</v>
+        <v>1847.9383648714791</v>
       </c>
       <c r="CK74" s="3">
         <f t="shared" si="103"/>
-        <v>730.9410526941067</v>
+        <v>1829.4589812227644</v>
       </c>
       <c r="CL74" s="3">
         <f t="shared" si="103"/>
-        <v>723.63164216716564</v>
+        <v>1811.1643914105366</v>
       </c>
       <c r="CM74" s="3">
         <f t="shared" si="103"/>
-        <v>716.39532574549401</v>
+        <v>1793.0527474964313</v>
       </c>
       <c r="CN74" s="3">
         <f t="shared" si="103"/>
-        <v>709.23137248803903</v>
+        <v>1775.122220021467</v>
       </c>
       <c r="CO74" s="3">
         <f t="shared" si="103"/>
-        <v>702.13905876315869</v>
+        <v>1757.3709978212523</v>
       </c>
       <c r="CP74" s="3">
         <f t="shared" si="103"/>
-        <v>695.11766817552711</v>
+        <v>1739.7972878430398</v>
       </c>
       <c r="CQ74" s="3">
         <f t="shared" si="103"/>
-        <v>688.16649149377179</v>
+        <v>1722.3993149646094</v>
       </c>
       <c r="CR74" s="3">
         <f t="shared" si="103"/>
-        <v>681.2848265788341</v>
+        <v>1705.1753218149634</v>
       </c>
       <c r="CS74" s="3">
         <f t="shared" si="103"/>
-        <v>674.47197831304572</v>
+        <v>1688.1235685968138</v>
       </c>
       <c r="CT74" s="3">
         <f t="shared" si="103"/>
-        <v>667.72725852991528</v>
+        <v>1671.2423329108456</v>
       </c>
       <c r="CU74" s="3">
         <f t="shared" si="103"/>
-        <v>661.04998594461608</v>
+        <v>1654.529909581737</v>
       </c>
       <c r="CV74" s="3">
         <f t="shared" si="103"/>
-        <v>654.43948608516996</v>
+        <v>1637.9846104859196</v>
       </c>
       <c r="CW74" s="3">
         <f t="shared" si="103"/>
-        <v>647.89509122431821</v>
+        <v>1621.6047643810605</v>
       </c>
       <c r="CX74" s="3">
         <f t="shared" ref="CX74:EJ74" si="104">CW74*(1+$AN$30)</f>
-        <v>641.41614031207507</v>
+        <v>1605.3887167372498</v>
       </c>
       <c r="CY74" s="3">
         <f t="shared" si="104"/>
-        <v>635.00197890895436</v>
+        <v>1589.3348295698772</v>
       </c>
       <c r="CZ74" s="3">
         <f t="shared" si="104"/>
-        <v>628.65195911986484</v>
+        <v>1573.4414812741784</v>
       </c>
       <c r="DA74" s="3">
         <f t="shared" si="104"/>
-        <v>622.36543952866623</v>
+        <v>1557.7070664614366</v>
       </c>
       <c r="DB74" s="3">
         <f t="shared" si="104"/>
-        <v>616.14178513337959</v>
+        <v>1542.1299957968222</v>
       </c>
       <c r="DC74" s="3">
         <f t="shared" si="104"/>
-        <v>609.98036728204579</v>
+        <v>1526.7086958388541</v>
       </c>
       <c r="DD74" s="3">
         <f t="shared" si="104"/>
-        <v>603.88056360922531</v>
+        <v>1511.4416088804655</v>
       </c>
       <c r="DE74" s="3">
         <f t="shared" si="104"/>
-        <v>597.8417579731331</v>
+        <v>1496.3271927916608</v>
       </c>
       <c r="DF74" s="3">
         <f t="shared" si="104"/>
-        <v>591.86334039340181</v>
+        <v>1481.3639208637442</v>
       </c>
       <c r="DG74" s="3">
         <f t="shared" si="104"/>
-        <v>585.94470698946782</v>
+        <v>1466.5502816551068</v>
       </c>
       <c r="DH74" s="3">
         <f t="shared" si="104"/>
-        <v>580.0852599195731</v>
+        <v>1451.8847788385558</v>
       </c>
       <c r="DI74" s="3">
         <f t="shared" si="104"/>
-        <v>574.28440732037734</v>
+        <v>1437.3659310501703</v>
       </c>
       <c r="DJ74" s="3">
         <f t="shared" si="104"/>
-        <v>568.5415632471736</v>
+        <v>1422.9922717396685</v>
       </c>
       <c r="DK74" s="3">
         <f t="shared" si="104"/>
-        <v>562.85614761470185</v>
+        <v>1408.7623490222718</v>
       </c>
       <c r="DL74" s="3">
         <f t="shared" si="104"/>
-        <v>557.22758613855478</v>
+        <v>1394.674725532049</v>
       </c>
       <c r="DM74" s="3">
         <f t="shared" si="104"/>
-        <v>551.65531027716918</v>
+        <v>1380.7279782767284</v>
       </c>
       <c r="DN74" s="3">
         <f t="shared" si="104"/>
-        <v>546.13875717439748</v>
+        <v>1366.920698493961</v>
       </c>
       <c r="DO74" s="3">
         <f t="shared" si="104"/>
-        <v>540.67736960265347</v>
+        <v>1353.2514915090214</v>
       </c>
       <c r="DP74" s="3">
         <f t="shared" si="104"/>
-        <v>535.27059590662691</v>
+        <v>1339.7189765939313</v>
       </c>
       <c r="DQ74" s="3">
         <f t="shared" si="104"/>
-        <v>529.91788994756064</v>
+        <v>1326.3217868279919</v>
       </c>
       <c r="DR74" s="3">
         <f t="shared" si="104"/>
-        <v>524.61871104808506</v>
+        <v>1313.0585689597119</v>
       </c>
       <c r="DS74" s="3">
         <f t="shared" si="104"/>
-        <v>519.37252393760423</v>
+        <v>1299.9279832701147</v>
       </c>
       <c r="DT74" s="3">
         <f t="shared" si="104"/>
-        <v>514.17879869822821</v>
+        <v>1286.9287034374136</v>
       </c>
       <c r="DU74" s="3">
         <f t="shared" si="104"/>
-        <v>509.0370107112459</v>
+        <v>1274.0594164030394</v>
       </c>
       <c r="DV74" s="3">
         <f t="shared" si="104"/>
-        <v>503.94664060413345</v>
+        <v>1261.318822239009</v>
       </c>
       <c r="DW74" s="3">
         <f t="shared" si="104"/>
-        <v>498.90717419809209</v>
+        <v>1248.7056340166189</v>
       </c>
       <c r="DX74" s="3">
         <f t="shared" si="104"/>
-        <v>493.91810245611117</v>
+        <v>1236.2185776764527</v>
       </c>
       <c r="DY74" s="3">
         <f t="shared" si="104"/>
-        <v>488.97892143155008</v>
+        <v>1223.8563918996881</v>
       </c>
       <c r="DZ74" s="3">
         <f t="shared" si="104"/>
-        <v>484.08913221723458</v>
+        <v>1211.6178279806911</v>
       </c>
       <c r="EA74" s="3">
         <f t="shared" si="104"/>
-        <v>479.24824089506222</v>
+        <v>1199.5016497008842</v>
       </c>
       <c r="EB74" s="3">
         <f t="shared" si="104"/>
-        <v>474.45575848611162</v>
+        <v>1187.5066332038753</v>
       </c>
       <c r="EC74" s="3">
         <f t="shared" si="104"/>
-        <v>469.71120090125049</v>
+        <v>1175.6315668718364</v>
       </c>
       <c r="ED74" s="3">
         <f t="shared" si="104"/>
-        <v>465.01408889223796</v>
+        <v>1163.8752512031181</v>
       </c>
       <c r="EE74" s="3">
         <f t="shared" si="104"/>
-        <v>460.36394800331556</v>
+        <v>1152.2364986910868</v>
       </c>
       <c r="EF74" s="3">
         <f t="shared" si="104"/>
-        <v>455.76030852328239</v>
+        <v>1140.714133704176</v>
       </c>
       <c r="EG74" s="3">
         <f t="shared" si="104"/>
-        <v>451.20270543804958</v>
+        <v>1129.3069923671342</v>
       </c>
       <c r="EH74" s="3">
         <f t="shared" si="104"/>
-        <v>446.69067838366908</v>
+        <v>1118.0139224434629</v>
       </c>
       <c r="EI74" s="3">
         <f t="shared" si="104"/>
-        <v>442.22377159983239</v>
+        <v>1106.8337832190282</v>
       </c>
       <c r="EJ74" s="3">
         <f t="shared" si="104"/>
-        <v>437.80153388383405</v>
+        <v>1095.7654453868379</v>
       </c>
     </row>
     <row r="77" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AN77" s="6">
         <f>NPV(AN31,Z74:EJ74)</f>
-        <v>511.96820024325359</v>
+        <v>10013.929248012633</v>
       </c>
     </row>
     <row r="78" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AN78" s="6">
         <f>Main!D8</f>
-        <v>3259</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="79" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AN79" s="6">
         <f>AN77+AN78</f>
-        <v>3770.9682002432537</v>
+        <v>12663.929248012633</v>
       </c>
     </row>
     <row r="80" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AN80" s="4">
         <f>AN79/AJ22</f>
-        <v>3.1077700677791769</v>
+        <v>10.330311810109007</v>
       </c>
     </row>
     <row r="81" spans="40:40" x14ac:dyDescent="0.3">
       <c r="AN81" s="4">
         <f>Main!D3</f>
-        <v>12.68</v>
+        <v>16.350000000000001</v>
       </c>
     </row>
     <row r="82" spans="40:40" x14ac:dyDescent="0.3">
       <c r="AN82" s="11">
         <f>AN80/AN81-1</f>
-        <v>-0.75490772336126366</v>
+        <v>-0.368176647699755</v>
+      </c>
+    </row>
+    <row r="83" spans="40:40" x14ac:dyDescent="0.3">
+      <c r="AN83" s="7" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
